--- a/115-1學期行事曆(1150828).xlsx
+++ b/115-1學期行事曆(1150828).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\163.16.121.157\115學年度\11填報區\01教務處填報區\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A95598-CE9F-4D81-B535-A4959BC2E336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E44129-308F-4DE0-85B4-348F1A62BB66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="420" windowWidth="27600" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
   <si>
     <t>年</t>
   </si>
@@ -591,11 +591,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>12/23(三)聖誕踩街
-12/25(五)-12/28(一)軟式聯賽高雄市賽</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>11/10(二)1-3年級野森動物學校外教學活動
 11/13(五)115學年校慶運動會暨園遊會暨家庭教育活動</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -613,10 +608,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>11/20(五)-11/23(一)2026原棒協關懷盃(台東)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>09/07（一）~9/11（五）測量身高體重視力
 09/08 (二) 全校第一次游泳課(屏東運動中心)
 09/09(三)教師研習-輔導管教及霸凌性平事件處理
@@ -643,6 +634,119 @@
   <si>
     <t>09/21(一)921國家防災日防災正式演練
 09/22(二)全校第三次游泳課(屏東運動中心)暨屏菸基地校外教學</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01/25(一)-01/29(五)南投縣法治國小歌謠與棒球交流</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11/11(三)頒發第一次定期評量優良獎
+11/11(三)教師研習-社群共課(雙語導覽員/SEL社會情緒)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>09/07(一)課後班正式開課(課照、學扶、夜光、專案)
+09/09(三)教師研習-輔導管教及霸凌性平事件處理
+09/12(六)AI學伴相見歡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12/23(三)聖誕踩街</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12/16(三)東方超捷到校贈送聖誕鞋盒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1/16(五)-1/18(一)軟式聯賽高雄市賽(岡山)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>幼生系統資料登錄/廚工加保/契約進用人員契約書簽訂
+教職員異動報局(廚工、學前特)
+混齡報局
+全園安全管理檢核(包含遊戲設施) 、飲水機定期維護
+期初教材教具、清潔用品添購
+全園性教保活動課程發展會議
+8/28課發會
+全園環境清潔消毒
+8/28(五)輔導員訪視</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">成立教保員考核小組/幼生團體保險辦理
+延長照顧調查及辦理
+幼兒學前補助款申請、收費、經費入庫、發放繳費收據
+期初園務會議/期初校務會議/幼兒發展篩檢/測量期初身高體重視力
+遠離腸病毒、新型狀冠病毒宣導(洗手時機及步驟)
+9/10班親會
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9/21(一)輔導員訪視</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全園安全管理檢核(包含遊戲設施) 、飲水機定期維護
+期初教材教具、清潔用品添購
+鑑定安置提報
+幼兒發展篩檢追蹤
+10/5(一) 輔導員訪視</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/21(三)輔導員訪視</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教保員平時考核</t>
+  </si>
+  <si>
+    <t>全園安全管理檢核(包含遊戲設施)、飲水機定期維護</t>
+  </si>
+  <si>
+    <t>流感防疫、咳嗽禮節、呼吸道保健宣導</t>
+  </si>
+  <si>
+    <t>幼兒發展篩檢追蹤
+11/18(三)輔導員訪視</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">公告115-2收退費基準
+全園安全管理檢核(包含遊戲設施)、飲水機定期維護、水質檢驗
+鑑定安置提報/年度關帳
+幼兒發展篩檢追蹤/事故傷害防制、健康飲食宣導
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>聖誕活動12/23(三)聖誕踩街</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全園安全管理檢核(包含遊戲設施)、飲水機定期維護
+測量期末身高體重
+預防諾羅病毒宣導
+幼兒發展篩檢追蹤
+期末校務會議
+期末園務會議</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01/20(三)休業式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>09/30 心理健康月活動</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11/20(五)-11/23(一)2026原棒協關懷盃(台東)
+11/21(六)我是小畫家繪畫比賽活動(寶來國小)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -670,23 +774,8 @@
       </rPr>
       <t>)下午流感疫苗施打
 10/21(三)科普列車體驗暨合唱團展演活動(高雄火車站)
-10/22(四)115學年高雄市原住民族歌謠比賽(翠屏國中小)</t>
+10/21(三)115學年高雄市原住民族歌謠比賽(翠屏國中小)</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>01/25(一)-01/29(五)南投縣法治國小歌謠與棒球交流</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11/11(三)頒發第一次定期評量優良獎
-11/11(三)教師研習-社群共課(雙語導覽員/SEL社會情緒)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>09/07(一)課後班正式開課(課照、學扶、夜光、專案)
-09/09(三)教師研習-輔導管教及霸凌性平事件處理
-09/12(六)AI學伴相見歡</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1387,10 +1476,12 @@
         <v>77</v>
       </c>
       <c r="G8" s="15" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H8" s="6"/>
-      <c r="I8" s="8"/>
+      <c r="I8" s="8" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="9" spans="2:9" ht="102" customHeight="1">
       <c r="B9" s="21"/>
@@ -1404,13 +1495,15 @@
         <v>64</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
+      <c r="I9" s="6" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="10" spans="2:9" ht="78" customHeight="1">
       <c r="B10" s="21"/>
@@ -1427,7 +1520,7 @@
         <v>87</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
@@ -1447,10 +1540,12 @@
         <v>88</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
+      <c r="I11" s="6" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="12" spans="2:9" ht="46.5" customHeight="1">
       <c r="B12" s="21"/>
@@ -1466,7 +1561,9 @@
       <c r="F12" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="G12" s="6"/>
+      <c r="G12" s="6" t="s">
+        <v>124</v>
+      </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
     </row>
@@ -1485,10 +1582,12 @@
         <v>90</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
+      <c r="I13" s="6" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="14" spans="2:9" ht="78.75">
       <c r="B14" s="21"/>
@@ -1503,7 +1602,7 @@
         <v>91</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
@@ -1521,10 +1620,12 @@
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="16" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="H15" s="12"/>
-      <c r="I15" s="6"/>
+      <c r="I15" s="6" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="16" spans="2:9" ht="81" customHeight="1">
       <c r="B16" s="21"/>
@@ -1541,7 +1642,7 @@
         <v>82</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="6"/>
@@ -1562,7 +1663,9 @@
       </c>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
+      <c r="I17" s="6" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="18" spans="2:9" ht="68.25" customHeight="1">
       <c r="B18" s="21"/>
@@ -1574,13 +1677,15 @@
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
+      <c r="I18" s="6" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="19" spans="2:9" ht="51" customHeight="1">
       <c r="B19" s="21"/>
@@ -1595,10 +1700,12 @@
         <v>84</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
+      <c r="I19" s="6" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="20" spans="2:9" ht="69.75" customHeight="1">
       <c r="B20" s="21"/>
@@ -1616,7 +1723,9 @@
       </c>
       <c r="G20" s="6"/>
       <c r="H20" s="11"/>
-      <c r="I20" s="6"/>
+      <c r="I20" s="6" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="21" spans="2:9" ht="81.75" customHeight="1">
       <c r="B21" s="21"/>
@@ -1650,7 +1759,9 @@
       </c>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
+      <c r="I22" s="6" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="23" spans="2:9" ht="66.75" customHeight="1">
       <c r="B23" s="21"/>
@@ -1664,7 +1775,9 @@
       <c r="F23" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="G23" s="6"/>
+      <c r="G23" s="6" t="s">
+        <v>109</v>
+      </c>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
     </row>
@@ -1683,10 +1796,12 @@
         <v>79</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
+      <c r="I24" s="6" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="25" spans="2:9" ht="53.25" customHeight="1">
       <c r="B25" s="21"/>
@@ -1736,9 +1851,13 @@
       <c r="F27" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="G27" s="6"/>
+      <c r="G27" s="6" t="s">
+        <v>110</v>
+      </c>
       <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
+      <c r="I27" s="6" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="28" spans="2:9" ht="66" customHeight="1">
       <c r="B28" s="21"/>
@@ -1756,7 +1875,9 @@
       </c>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
+      <c r="I28" s="6" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="29" spans="2:9" ht="75" customHeight="1">
       <c r="B29" s="21"/>
@@ -1769,7 +1890,7 @@
         <v>96</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="6"/>
